--- a/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort3.xlsx
+++ b/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure 3\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12644FB-83DC-437F-BFDA-C1B5E0F177DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77345370-31C8-44E5-BBB5-400C1AED15E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A514A187-A7D1-4A2E-BBE9-38EB1CA0002D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="36">
   <si>
     <t>Weight</t>
   </si>
@@ -2806,7 +2806,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2351EE4F-5BCF-49F0-BB77-4C4BF594B1E4}">
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4660,6 +4660,108 @@
       </c>
       <c r="E109">
         <v>183</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>11</v>
+      </c>
+      <c r="B110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111">
+        <v>15</v>
+      </c>
+      <c r="E111">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>11</v>
+      </c>
+      <c r="B112" t="s">
+        <v>27</v>
+      </c>
+      <c r="C112" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112">
+        <v>30</v>
+      </c>
+      <c r="E112">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>11</v>
+      </c>
+      <c r="B113" t="s">
+        <v>27</v>
+      </c>
+      <c r="C113" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113">
+        <v>60</v>
+      </c>
+      <c r="E113">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>11</v>
+      </c>
+      <c r="B114" t="s">
+        <v>27</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114">
+        <v>90</v>
+      </c>
+      <c r="E114">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115">
+        <v>120</v>
+      </c>
+      <c r="E115">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
